--- a/output/pdf_financials_xlsx/VLX.xlsx
+++ b/output/pdf_financials_xlsx/VLX.xlsx
@@ -4288,19 +4288,19 @@
         <v>1.354528</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>1.44948</v>
+        <v>1.636356</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>1.516555</v>
+        <v>2.885256</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>1.677037</v>
+        <v>4.158479</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>2.295156</v>
+        <v>4.434469</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>3.856707</v>
+        <v>4.434469</v>
       </c>
     </row>
     <row r="93">
@@ -7312,7 +7312,11 @@
           <t>Warrants reserve 11</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
@@ -7372,7 +7376,11 @@
           <t>Share based payments reserve 12</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/VLX.xlsx
+++ b/output/pdf_financials_xlsx/VLX.xlsx
@@ -2041,19 +2041,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.105545</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.058226</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.319314</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.385137</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.193446</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>0.065886</v>
@@ -2115,19 +2115,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.105545</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.058226</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.00135</v>
+        <v>0.320664</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.000165</v>
+        <v>0.385302</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.193446</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>0.145386</v>
@@ -2565,13 +2565,13 @@
         <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.336214</v>
+        <v>0.0169</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.387122</v>
+        <v>0.001985</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.211552</v>
+        <v>0.018106</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>0.005029</v>
@@ -5461,10 +5461,10 @@
         <v>0</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>0</v>
+        <v>-0.017921</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>0</v>
+        <v>-0.007567</v>
       </c>
     </row>
     <row r="125">
@@ -5498,10 +5498,10 @@
         <v>0</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>0</v>
+        <v>-0.017921</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>0</v>
+        <v>-0.007567</v>
       </c>
     </row>
     <row r="126">
@@ -12140,7 +12140,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -15272,7 +15272,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E145" s="5" t="n">
@@ -18568,7 +18568,11 @@
           <t>Lease payment</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr"/>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E196" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/VLX.xlsx
+++ b/output/pdf_financials_xlsx/VLX.xlsx
@@ -1512,10 +1512,8 @@
       <c r="D23" s="3" t="n">
         <v>0.547862</v>
       </c>
-      <c r="E23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E23" s="3" t="n">
+        <v>-0.374946</v>
       </c>
       <c r="F23" s="1" t="inlineStr">
         <is>
@@ -3211,10 +3209,10 @@
         <v>0</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>0.18923</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>0.08376400000000001</v>
       </c>
     </row>
     <row r="65">
@@ -3304,28 +3302,28 @@
         <v>0</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.027403</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.019862</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.016</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.022</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.024</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.081385</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.07932</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.092029</v>
       </c>
     </row>
     <row r="68">
@@ -3356,13 +3354,13 @@
         <v>0.315621</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>0</v>
+        <v>0.081385</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0</v>
+        <v>0.26855</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>0</v>
+        <v>0.175793</v>
       </c>
     </row>
     <row r="69">
@@ -3615,7 +3613,7 @@
         <v>0</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>0.19688</v>
+        <v>0.115495</v>
       </c>
       <c r="J75" s="3" t="n">
         <v>0</v>
@@ -4514,10 +4512,8 @@
       <c r="D99" s="3" t="n">
         <v>0.547862</v>
       </c>
-      <c r="E99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E99" s="3" t="n">
+        <v>-0.374946</v>
       </c>
       <c r="F99" s="1" t="inlineStr">
         <is>
@@ -5108,22 +5104,22 @@
         <v>0</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.373079</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>0.001185</v>
       </c>
       <c r="F115" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0</v>
+        <v>0.04447</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>0.000125</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="J115" s="3" t="n">
         <v>0</v>
@@ -19610,7 +19606,11 @@
           <t>Proceeds on sale of marketable securities 7</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr"/>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E212" t="inlineStr">
         <is>
           <t>-</t>
@@ -21060,7 +21060,11 @@
           <t>Proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr"/>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr">
         <is>
           <t>-</t>
@@ -21990,7 +21994,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D248" t="inlineStr"/>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E248" t="inlineStr">
         <is>
           <t>-</t>
